--- a/data/trans_orig/IP19_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP19_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8982</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18332</t>
+          <t>18245</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19302</t>
+          <t>19947</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20416</t>
+          <t>20371</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35183</t>
+          <t>34539</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34236</t>
+          <t>34323</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43586</t>
+          <t>43835</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40915</t>
+          <t>40270</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51158</t>
+          <t>51075</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77602</t>
+          <t>78246</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>92369</t>
+          <t>92414</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,94%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24995</t>
+          <t>25075</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39945</t>
+          <t>40001</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28703</t>
+          <t>28637</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44198</t>
+          <t>44639</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58907</t>
+          <t>57574</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79703</t>
+          <t>79400</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61617</t>
+          <t>61561</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76567</t>
+          <t>76487</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64559</t>
+          <t>64118</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80054</t>
+          <t>80120</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>130616</t>
+          <t>130919</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>151412</t>
+          <t>152745</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>72,63%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19389</t>
+          <t>19756</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32523</t>
+          <t>32983</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19865</t>
+          <t>19096</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31786</t>
+          <t>31701</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42938</t>
+          <t>42551</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60740</t>
+          <t>61152</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,56%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34383</t>
+          <t>33923</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47517</t>
+          <t>47150</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38541</t>
+          <t>38626</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50462</t>
+          <t>51231</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76493</t>
+          <t>76081</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>94295</t>
+          <t>94682</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,99%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16534</t>
+          <t>17503</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30353</t>
+          <t>30122</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22941</t>
+          <t>22797</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36977</t>
+          <t>36738</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44994</t>
+          <t>44104</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63640</t>
+          <t>62558</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>40,63%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44508</t>
+          <t>44739</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58327</t>
+          <t>57358</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42134</t>
+          <t>42373</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56170</t>
+          <t>56314</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>90332</t>
+          <t>91414</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>108978</t>
+          <t>109868</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>71,36%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16484</t>
+          <t>16186</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26634</t>
+          <t>26387</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9720</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19717</t>
+          <t>20230</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28389</t>
+          <t>27482</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43146</t>
+          <t>43342</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>49,99%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15218</t>
+          <t>15465</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25368</t>
+          <t>25666</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25126</t>
+          <t>24613</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35123</t>
+          <t>35038</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43549</t>
+          <t>43353</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58306</t>
+          <t>59213</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>68,3%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19806</t>
+          <t>19749</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10912</t>
+          <t>10942</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21034</t>
+          <t>21526</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22902</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38041</t>
+          <t>37397</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36249</t>
+          <t>36306</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46861</t>
+          <t>46853</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38698</t>
+          <t>38206</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48820</t>
+          <t>48790</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>77746</t>
+          <t>78390</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>92885</t>
+          <t>93283</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,56%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37601</t>
+          <t>37913</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54732</t>
+          <t>56633</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31043</t>
+          <t>31577</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49173</t>
+          <t>49079</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>73688</t>
+          <t>73409</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>97820</t>
+          <t>98181</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>73890</t>
+          <t>71989</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>91021</t>
+          <t>90709</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>86482</t>
+          <t>86576</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>104612</t>
+          <t>104078</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>166457</t>
+          <t>166096</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>190589</t>
+          <t>190868</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,22%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36602</t>
+          <t>36258</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54948</t>
+          <t>54442</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27933</t>
+          <t>27689</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45247</t>
+          <t>44080</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>69313</t>
+          <t>69204</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>93441</t>
+          <t>94255</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>102956</t>
+          <t>103462</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>121302</t>
+          <t>121646</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>118811</t>
+          <t>119978</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>136125</t>
+          <t>136369</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>228521</t>
+          <t>227707</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>252649</t>
+          <t>252758</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,51%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>200664</t>
+          <t>200706</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>240991</t>
+          <t>241117</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>193080</t>
+          <t>193317</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>233369</t>
+          <t>231790</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>405580</t>
+          <t>408337</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>464739</t>
+          <t>462948</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>439339</t>
+          <t>439213</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>479666</t>
+          <t>479624</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>489331</t>
+          <t>490910</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>529620</t>
+          <t>529383</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>938291</t>
+          <t>940082</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>997450</t>
+          <t>994693</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,9%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11100</t>
+          <t>10835</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22274</t>
+          <t>22096</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10568</t>
+          <t>10787</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22435</t>
+          <t>21965</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24171</t>
+          <t>24603</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40226</t>
+          <t>40182</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35153</t>
+          <t>35331</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46327</t>
+          <t>46592</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41161</t>
+          <t>41631</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53028</t>
+          <t>52809</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80797</t>
+          <t>80841</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96852</t>
+          <t>96420</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,67%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26723</t>
+          <t>26765</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43272</t>
+          <t>42023</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28678</t>
+          <t>28255</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44899</t>
+          <t>43909</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58347</t>
+          <t>58011</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80719</t>
+          <t>80048</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61441</t>
+          <t>62690</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>77990</t>
+          <t>77948</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>66260</t>
+          <t>67250</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82481</t>
+          <t>82904</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>135153</t>
+          <t>135824</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>157525</t>
+          <t>157861</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>73,13%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17171</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30565</t>
+          <t>30256</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16871</t>
+          <t>17506</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30399</t>
+          <t>30100</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37745</t>
+          <t>37306</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56907</t>
+          <t>57245</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,28%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37613</t>
+          <t>37922</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51007</t>
+          <t>51489</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40111</t>
+          <t>40410</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53639</t>
+          <t>53004</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>81781</t>
+          <t>81443</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>100943</t>
+          <t>101382</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>73,1%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18076</t>
+          <t>17496</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31643</t>
+          <t>31111</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16217</t>
+          <t>16064</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31609</t>
+          <t>30139</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37185</t>
+          <t>37946</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57679</t>
+          <t>56985</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,72%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46118</t>
+          <t>46650</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59685</t>
+          <t>60265</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50181</t>
+          <t>51651</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65573</t>
+          <t>65726</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>101872</t>
+          <t>102566</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>122366</t>
+          <t>121605</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,22%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12689</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23478</t>
+          <t>23502</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>11806</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22542</t>
+          <t>22751</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27237</t>
+          <t>27398</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42440</t>
+          <t>43042</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,48%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20423</t>
+          <t>20399</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31212</t>
+          <t>31826</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24210</t>
+          <t>24001</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34865</t>
+          <t>34946</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48213</t>
+          <t>47611</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63416</t>
+          <t>63255</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>69,78%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12171</t>
+          <t>12053</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23876</t>
+          <t>23585</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14875</t>
+          <t>14861</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27158</t>
+          <t>27392</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29748</t>
+          <t>29174</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47054</t>
+          <t>46826</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,29%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32109</t>
+          <t>32400</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43814</t>
+          <t>43932</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33087</t>
+          <t>32853</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45370</t>
+          <t>45384</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>69176</t>
+          <t>69404</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>86482</t>
+          <t>87056</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,9%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32863</t>
+          <t>33629</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51525</t>
+          <t>51377</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38404</t>
+          <t>38777</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56123</t>
+          <t>57287</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>75826</t>
+          <t>76962</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>101905</t>
+          <t>103234</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,42%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>87193</t>
+          <t>87341</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>105855</t>
+          <t>105089</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>88631</t>
+          <t>87467</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>106350</t>
+          <t>105977</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>181567</t>
+          <t>180238</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>207646</t>
+          <t>206510</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>72,85%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>35634</t>
+          <t>35681</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54716</t>
+          <t>54104</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28116</t>
+          <t>26920</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45513</t>
+          <t>44020</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>67986</t>
+          <t>67021</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94139</t>
+          <t>93001</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>109992</t>
+          <t>110604</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>129074</t>
+          <t>129027</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>125080</t>
+          <t>126573</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>142477</t>
+          <t>143673</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>241162</t>
+          <t>242300</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>267315</t>
+          <t>268280</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>80,01%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>199907</t>
+          <t>198122</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>239439</t>
+          <t>237449</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>197577</t>
+          <t>197011</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>237848</t>
+          <t>237214</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>408588</t>
+          <t>409967</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>463892</t>
+          <t>468490</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>471952</t>
+          <t>473942</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>511484</t>
+          <t>513269</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>511552</t>
+          <t>512186</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>551823</t>
+          <t>552389</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>996899</t>
+          <t>992301</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1052203</t>
+          <t>1050824</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,94%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15371</t>
+          <t>16425</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27828</t>
+          <t>27917</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12934</t>
+          <t>13098</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25417</t>
+          <t>25295</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31650</t>
+          <t>32369</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48855</t>
+          <t>49200</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,38%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29543</t>
+          <t>29454</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42000</t>
+          <t>40946</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39045</t>
+          <t>39167</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51528</t>
+          <t>51364</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72978</t>
+          <t>72633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90183</t>
+          <t>89464</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,43%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23214</t>
+          <t>23167</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39356</t>
+          <t>38072</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26288</t>
+          <t>26536</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42237</t>
+          <t>42182</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53439</t>
+          <t>53564</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75572</t>
+          <t>75243</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,12%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64591</t>
+          <t>65875</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80733</t>
+          <t>80780</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68046</t>
+          <t>68101</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83995</t>
+          <t>83747</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>138658</t>
+          <t>138987</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>160791</t>
+          <t>160666</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,0%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8913</t>
+          <t>9285</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20699</t>
+          <t>21078</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9822</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22060</t>
+          <t>21140</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38025</t>
+          <t>38500</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,16%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46132</t>
+          <t>45753</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57918</t>
+          <t>57546</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47845</t>
+          <t>48765</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60083</t>
+          <t>59746</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>98711</t>
+          <t>98236</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>114696</t>
+          <t>114487</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,73%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24983</t>
+          <t>24528</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38689</t>
+          <t>39151</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23131</t>
+          <t>24148</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38809</t>
+          <t>38422</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52077</t>
+          <t>52459</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73875</t>
+          <t>73351</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,38%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38272</t>
+          <t>37810</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51978</t>
+          <t>52433</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42375</t>
+          <t>42762</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58053</t>
+          <t>57036</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>84270</t>
+          <t>84794</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>106068</t>
+          <t>105686</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,83%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12264</t>
+          <t>12245</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5747</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15140</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11486</t>
+          <t>11875</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24593</t>
+          <t>23599</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31174</t>
+          <t>31193</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39558</t>
+          <t>39495</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31210</t>
+          <t>31249</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40947</t>
+          <t>40603</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65195</t>
+          <t>66189</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78302</t>
+          <t>77913</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>86,77%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21399</t>
+          <t>21149</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33384</t>
+          <t>33728</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24714</t>
+          <t>24791</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37833</t>
+          <t>37612</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49496</t>
+          <t>49578</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>66737</t>
+          <t>67715</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>60,45%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20889</t>
+          <t>20545</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32874</t>
+          <t>33124</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>20127</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33025</t>
+          <t>32948</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>45275</t>
+          <t>44297</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>62516</t>
+          <t>62434</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,74%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34481</t>
+          <t>33694</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52430</t>
+          <t>51399</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24418</t>
+          <t>24182</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41424</t>
+          <t>40686</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63960</t>
+          <t>63711</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87452</t>
+          <t>87778</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>84944</t>
+          <t>85975</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>102893</t>
+          <t>103680</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>102648</t>
+          <t>103386</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>119654</t>
+          <t>119890</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>193994</t>
+          <t>193668</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>217486</t>
+          <t>217735</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,36%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30009</t>
+          <t>30110</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46001</t>
+          <t>46927</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30947</t>
+          <t>31408</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>48964</t>
+          <t>49087</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>64596</t>
+          <t>64999</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>89482</t>
+          <t>89329</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>118175</t>
+          <t>117249</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>134167</t>
+          <t>134066</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>121885</t>
+          <t>121762</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>139902</t>
+          <t>139441</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>245543</t>
+          <t>245696</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>270429</t>
+          <t>270026</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,6%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>193627</t>
+          <t>192453</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>234321</t>
+          <t>231535</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>191404</t>
+          <t>189228</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>233289</t>
+          <t>230300</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>394224</t>
+          <t>396190</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>455617</t>
+          <t>453203</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>470050</t>
+          <t>472836</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>510744</t>
+          <t>511918</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>511555</t>
+          <t>514544</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>553440</t>
+          <t>555616</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>993598</t>
+          <t>996012</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1054991</t>
+          <t>1053025</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,66%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16217</t>
+          <t>16588</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31545</t>
+          <t>31440</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14327</t>
+          <t>13903</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29223</t>
+          <t>29370</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34868</t>
+          <t>35410</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56506</t>
+          <t>56401</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41737</t>
+          <t>41842</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57065</t>
+          <t>56694</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50143</t>
+          <t>49996</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65039</t>
+          <t>65463</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96142</t>
+          <t>96247</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117780</t>
+          <t>117238</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>76,8%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14450</t>
+          <t>13544</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41528</t>
+          <t>41805</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26430</t>
+          <t>27570</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49903</t>
+          <t>50131</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44020</t>
+          <t>45839</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83506</t>
+          <t>84032</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81541</t>
+          <t>81264</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>108619</t>
+          <t>109525</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73942</t>
+          <t>73714</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>97415</t>
+          <t>96275</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>163408</t>
+          <t>162882</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>202894</t>
+          <t>201075</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>81,44%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13628</t>
+          <t>13836</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24475</t>
+          <t>24615</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14300</t>
+          <t>14650</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26403</t>
+          <t>26671</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31119</t>
+          <t>30998</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48706</t>
+          <t>47589</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>38,39%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33058</t>
+          <t>32918</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43905</t>
+          <t>43697</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40010</t>
+          <t>39742</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52113</t>
+          <t>51763</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75240</t>
+          <t>76357</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>92827</t>
+          <t>92948</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,99%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19926</t>
+          <t>20171</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34576</t>
+          <t>34651</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23313</t>
+          <t>24784</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51438</t>
+          <t>54142</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49036</t>
+          <t>49208</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82932</t>
+          <t>83144</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,75%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34758</t>
+          <t>34683</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49408</t>
+          <t>49163</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25729</t>
+          <t>23025</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53854</t>
+          <t>52383</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63568</t>
+          <t>63356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>97464</t>
+          <t>97292</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,41%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11695</t>
+          <t>11707</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16909</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25834</t>
+          <t>25462</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,09%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22818</t>
+          <t>22806</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29735</t>
+          <t>29854</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23267</t>
+          <t>23528</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32080</t>
+          <t>32287</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48855</t>
+          <t>49227</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10575</t>
+          <t>10518</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20943</t>
+          <t>20945</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9752</t>
+          <t>10294</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20647</t>
+          <t>20580</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23461</t>
+          <t>23144</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37358</t>
+          <t>37855</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,98%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25224</t>
+          <t>25222</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35592</t>
+          <t>35649</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35539</t>
+          <t>35606</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46434</t>
+          <t>45892</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>64995</t>
+          <t>64498</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>78892</t>
+          <t>79209</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,39%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36772</t>
+          <t>36456</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55297</t>
+          <t>55728</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51985</t>
+          <t>52145</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77762</t>
+          <t>79136</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>95514</t>
+          <t>96381</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>127788</t>
+          <t>128139</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,71%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>67006</t>
+          <t>66575</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>85531</t>
+          <t>85847</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>74251</t>
+          <t>72877</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>100028</t>
+          <t>99868</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>146529</t>
+          <t>146178</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>178803</t>
+          <t>177936</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>64,87%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14267</t>
+          <t>14521</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28246</t>
+          <t>29841</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21398</t>
+          <t>21520</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39369</t>
+          <t>39201</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39511</t>
+          <t>39711</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61885</t>
+          <t>62966</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>100729</t>
+          <t>99134</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>114708</t>
+          <t>114454</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>115836</t>
+          <t>116004</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>133807</t>
+          <t>133685</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>222295</t>
+          <t>221214</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>244669</t>
+          <t>244469</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,03%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>162474</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>211914</t>
+          <t>212413</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>210840</t>
+          <t>210294</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>268717</t>
+          <t>266762</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>384559</t>
+          <t>384336</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>459488</t>
+          <t>461143</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>443261</t>
+          <t>442762</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>492701</t>
+          <t>495075</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>481654</t>
+          <t>483609</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>539531</t>
+          <t>540077</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>946058</t>
+          <t>944403</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1020987</t>
+          <t>1021210</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,66%</t>
         </is>
       </c>
     </row>
